--- a/Inventory_batch02.xlsx
+++ b/Inventory_batch02.xlsx
@@ -438,14 +438,14 @@
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="35" customWidth="1" min="18" max="18"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="35" customWidth="1" min="20" max="20"/>
+    <col width="40" customWidth="1" min="20" max="20"/>
     <col width="55" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="16" customWidth="1" min="23" max="23"/>
@@ -469,7 +469,7 @@
     <col width="16" customWidth="1" min="41" max="41"/>
     <col width="16" customWidth="1" min="42" max="42"/>
     <col width="16" customWidth="1" min="43" max="43"/>
-    <col width="90" customWidth="1" min="44" max="44"/>
+    <col width="95" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -746,15 +746,35 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Ranch Brook; South Creek; South Watershed; South river</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>42; 60; 178; 256</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>E; M</t>
+        </is>
+      </c>
       <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>(Perched) WT/GW dynamics and changes in GW storage; Return flow/interflow; SubFlow</t>
+        </is>
+      </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
           <t>N</t>
@@ -837,12 +857,12 @@
       </c>
       <c r="AI2" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AK2" s="2" t="inlineStr">
@@ -882,7 +902,7 @@
       </c>
       <c r="AR2" s="2" t="inlineStr">
         <is>
-          <t>OSTI/government reports describe three intensely gauged Upper Fourmile Creek/Savannah River Site watersheds (R, B, C) with meteorology, stream discharge, soil-water/soil-moisture modeling support, and well-level/groundwater observations. No official downloadable original experimental dataset was identified during this search.</t>
+          <t>OSTI/government reports describe three intensely gauged Upper Fourmile Creek/Savannah River Site watersheds (R, B, C) with meteorology, stream discharge, soil-water/soil-moisture modeling support, and well-level/groundwater observations. No official downloadable original experimental dataset was identified during this search. Penna supporting match: Ranch Brook; South Creek; South Watershed; South river (Clark et al., 2017; Donnelly et al., 1999; Moore et al., 1997; Wemple et al., 2007); Penna evidence was used only for Observed flags, not public access.</t>
         </is>
       </c>
     </row>
@@ -938,14 +958,30 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Brugga</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
       <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="R3" s="2" t="inlineStr"/>
       <c r="S3" s="2" t="inlineStr">
         <is>
@@ -1064,7 +1100,7 @@
       </c>
       <c r="AP3" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AQ3" s="2" t="inlineStr">
@@ -1074,7 +1110,7 @@
       </c>
       <c r="AR3" s="2" t="inlineStr">
         <is>
-          <t>Brugga studies document precipitation, discharge, snow-influenced runoff, wells/groundwater, saturated source areas, and 18O/3H/chloride/silica tracer hydrograph separation. Regional LUBW/University sources indicate some gauge/project data access, but no open complete experimental dataset was verified.</t>
+          <t>Brugga studies document precipitation, discharge, snow-influenced runoff, wells/groundwater, saturated source areas, and 18O/3H/chloride/silica tracer hydrograph separation. Regional LUBW/University sources indicate some gauge/project data access, but no open complete experimental dataset was verified. Penna supporting match: Brugga (Garvelmann et al., 2015); Penna evidence was used only for Observed flags, not public access.</t>
         </is>
       </c>
     </row>
@@ -1130,15 +1166,35 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shale Hills </t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>49; 100; 159; 160; 216; 240; 241</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>E; E+M; M</t>
+        </is>
+      </c>
       <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>S; S+SS; SS</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>(Perched) WT/GW dynamics and changes in GW storage; Groundwater - streamflow threshold; IEOF; Lateral flow; Macropore flow (no specifical vert/lat); Matrix flow; Pipe flow; Preferential flow (no specifica vert/lat); Return flow/interflow; Soil moisture -groundwater threshold; Soil moisture and rainfall -streamflow threshold; Soil moisture- streamflow threshold; SubFlow; Subsurface hillslope-stream connectivity; Vertical flow; Vertical preferential flow; Water movement through bedrock or at the soil/bedrock interface (either SubFlow or GW rise)</t>
+        </is>
+      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1146,7 +1202,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>CZO Archive / CUAHSI HydroShare Shale Hills CZO</t>
+          <t>CUAHSI HydroShare Shale Hills CZO - Garner Run</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -1171,12 +1227,12 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1211,32 +1267,32 @@
       </c>
       <c r="AG4" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AI4" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AK4" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
@@ -1251,22 +1307,22 @@
       </c>
       <c r="AO4" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AP4" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AQ4" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AR4" s="2" t="inlineStr">
         <is>
-          <t>HydroShare/CZO records for Garner Run provide public GroundHOG soil moisture, soil EC and temperature at 3 depths and CZO pages list precipitation plus well/porewater/stream chemistry resources. A public Garner Run discharge time series and isotope dataset were not verified.</t>
+          <t>HydroShare/CZO records for Garner Run provide public GroundHOG soil moisture, soil EC and temperature at 3 depths and CZO pages list precipitation plus well/porewater/stream chemistry resources. A public Garner Run discharge time series and isotope dataset were not verified. Penna supporting match: Shale Hills  (Lin et al., 2006a; Lin et al., 2006b; Curtu et al., 2014; Guo et al., 2018; Scaife et al., 2020; Tang et al., 2020); Penna evidence was used only for Observed flags, not public access. Official/project source override applied for public-data status.</t>
         </is>
       </c>
     </row>
@@ -1322,15 +1378,35 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shale Hills </t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>49; 100; 159; 160; 216; 240; 241</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>E; E+M; M</t>
+        </is>
+      </c>
       <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>S; S+SS; SS</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>(Perched) WT/GW dynamics and changes in GW storage; Groundwater - streamflow threshold; IEOF; Lateral flow; Macropore flow (no specifical vert/lat); Matrix flow; Pipe flow; Preferential flow (no specifica vert/lat); Return flow/interflow; Soil moisture -groundwater threshold; Soil moisture and rainfall -streamflow threshold; Soil moisture- streamflow threshold; SubFlow; Subsurface hillslope-stream connectivity; Vertical flow; Vertical preferential flow; Water movement through bedrock or at the soil/bedrock interface (either SubFlow or GW rise)</t>
+        </is>
+      </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1338,7 +1414,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>CZO Archive / CUAHSI HydroShare Shale Hills CZO</t>
+          <t>CUAHSI HydroShare Shale Hills CZO - Cole Farm</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -1363,12 +1439,12 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1403,32 +1479,32 @@
       </c>
       <c r="AG5" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AI5" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AK5" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
@@ -1443,22 +1519,22 @@
       </c>
       <c r="AO5" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AP5" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AQ5" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AR5" s="2" t="inlineStr">
         <is>
-          <t>HydroShare/CZO records for Cole Farm provide public precipitation, soil moisture, soil conductivity/EC and temperature at 4 depths, and groundwater depth/temperature resources. No public stream discharge or isotope series was verified for this agricultural site.</t>
+          <t>HydroShare/CZO records for Cole Farm provide public precipitation, soil moisture, soil conductivity/EC and temperature at 4 depths, and groundwater depth/temperature resources. No public stream discharge or isotope series was verified for this agricultural site. Penna supporting match: Shale Hills  (Lin et al., 2006a; Lin et al., 2006b; Curtu et al., 2014; Guo et al., 2018; Scaife et al., 2020; Tang et al., 2020); Penna evidence was used only for Observed flags, not public access. Official/project source override applied for public-data status.</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1590,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
+          <t>No high-confidence match</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr"/>
@@ -1530,7 +1606,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>GFZ/FID GEO and CAMELS-LUX / Luxembourg hydrometric data</t>
+          <t>GFZ/FID GEO / Luxembourg hydrometric datasets</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1650,7 +1726,7 @@
       </c>
       <c r="AR6" s="2" t="inlineStr">
         <is>
-          <t>Attert/Colpach sources document 15-min discharge for the Colpach subcatchment and hydrometeorological data products; later Luxembourg isotope studies report precipitation and stream-water isotope sampling. Soil moisture in CAMELS-LUX appears reanalysis-derived, not direct catchment observation, so it is not counted as observed.</t>
+          <t>Attert/Colpach sources document 15-min discharge for the Colpach subcatchment and hydrometeorological data products; later Luxembourg isotope studies report precipitation and stream-water isotope sampling. Soil moisture in CAMELS-LUX appears reanalysis-derived, not direct catchment observation, so it is not counted as observed. No high-confidence Penna catchment match found in available Part2 fuzzy matching. Official/project source override applied for public-data status.</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1782,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
+          <t>No high-confidence match</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr"/>
@@ -1722,7 +1798,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>GFZ/FID GEO and CAMELS-LUX / Luxembourg hydrometric data</t>
+          <t>GFZ/FID GEO / Luxembourg hydrometric datasets</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1842,7 +1918,7 @@
       </c>
       <c r="AR7" s="2" t="inlineStr">
         <is>
-          <t>Attert/Wollefsbach sources document 15-min discharge for Wollefsbach and Luxembourg hydrometeorological data products; isotope studies report precipitation and stream-water isotope sampling in nested catchments. Direct soil-moisture, groundwater, or EC observations were not verified.</t>
+          <t>Attert/Wollefsbach sources document 15-min discharge for Wollefsbach and Luxembourg hydrometeorological data products; isotope studies report precipitation and stream-water isotope sampling in nested catchments. Direct soil-moisture, groundwater, or EC observations were not verified. No high-confidence Penna catchment match found in available Part2 fuzzy matching. Official/project source override applied for public-data status.</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1974,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
+          <t>No high-confidence match</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr"/>
@@ -2034,7 +2110,7 @@
       </c>
       <c r="AR8" s="2" t="inlineStr">
         <is>
-          <t>Eel CZO HydroShare/CZO Archive provide public Angelo/Rivendell datasets for precipitation, South Fork Eel discharge, soil/rock moisture, groundwater depth, chemistry, EC, and stable isotopes from rainfall, stream, well, soil and stem water. No snow/SWE monitoring was identified.</t>
+          <t>Eel CZO HydroShare/CZO Archive provide public Angelo/Rivendell datasets for precipitation, South Fork Eel discharge, soil/rock moisture, groundwater depth, chemistry, EC, and stable isotopes from rainfall, stream, well, soil and stem water. No snow/SWE monitoring was identified. No high-confidence Penna catchment match found in available Part2 fuzzy matching.</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2166,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
+          <t>No high-confidence match</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
@@ -2226,7 +2302,7 @@
       </c>
       <c r="AR9" s="2" t="inlineStr">
         <is>
-          <t>CZO Archive describes Sagehorn-Russell Ranch as an Eel CZO field area with a weather station and monitored wells by permission of the landowner. Direct public downloads for Sagehorn-specific discharge, soil moisture, isotope, or EC data were not verified.</t>
+          <t>CZO Archive describes Sagehorn-Russell Ranch as an Eel CZO field area with a weather station and monitored wells by permission of the landowner. Direct public downloads for Sagehorn-specific discharge, soil moisture, isotope, or EC data were not verified. No high-confidence Penna catchment match found in available Part2 fuzzy matching.</t>
         </is>
       </c>
     </row>
@@ -2282,15 +2358,39 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Maimai M8; Maimai M13; Maimai M14; Maimai M15; Maimai M5; Maimai M6; Maimai M7; Maimai M9</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>169; 170</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>E+M</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Iso+Ions+EC+Dyes</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>S+SS</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>(Perched) WT/GW dynamics and changes in GW storage; Dynamics of saturated areas; Groundwater - streamflow threshold; Lateral flow; Matrix flow; Pipe flow; Preferential flow (no specifica vert/lat); SEOF; Soil moisture-subsurface flow threshold; SubFlow; Vertical flow; Water movement through bedrock or at the soil/bedrock interface (either SubFlow or GW rise)</t>
+        </is>
+      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2363,22 +2463,22 @@
       </c>
       <c r="AG10" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AH10" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AI10" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AJ10" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AK10" s="2" t="inlineStr">
@@ -2398,7 +2498,7 @@
       </c>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="AO10" s="2" t="inlineStr">
@@ -2418,7 +2518,7 @@
       </c>
       <c r="AR10" s="2" t="inlineStr">
         <is>
-          <t>Public Maimai HydroShare database includes M8 rainfall-runoff, isotope, soil-water matric potential, water-table/well, trench-flow/tracer and geochemical data from published studies.</t>
+          <t>Public Maimai HydroShare database includes M8 rainfall-runoff, isotope, soil-water matric potential, water-table/well, trench-flow/tracer and geochemical data from published studies. Penna supporting match: Maimai M8; Maimai M13; Maimai M14; Maimai M15; Maimai M5; Maimai M6; Maimai M7; Maimai M9 (McGlynn et al., 2002; McGlynn et al., 2002; McDonnell etal., 2021); Penna evidence was used only for Observed flags, not public access. Official/project source override applied for public-data status.</t>
         </is>
       </c>
     </row>
@@ -2474,15 +2574,39 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Maimai M13; Maimai M14; Maimai M15; Maimai M5; Maimai M6; Maimai M7; Maimai M8; Maimai M9</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>169; 170</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>E+M</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Iso+Ions+EC+Dyes</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>S+SS</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>(Perched) WT/GW dynamics and changes in GW storage; Dynamics of saturated areas; Groundwater - streamflow threshold; Lateral flow; Matrix flow; Pipe flow; Preferential flow (no specifica vert/lat); SEOF; Soil moisture-subsurface flow threshold; SubFlow; Vertical flow; Water movement through bedrock or at the soil/bedrock interface (either SubFlow or GW rise)</t>
+        </is>
+      </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2555,22 +2679,22 @@
       </c>
       <c r="AG11" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AH11" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AI11" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AJ11" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AK11" s="2" t="inlineStr">
@@ -2590,7 +2714,7 @@
       </c>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="AO11" s="2" t="inlineStr">
@@ -2610,7 +2734,7 @@
       </c>
       <c r="AR11" s="2" t="inlineStr">
         <is>
-          <t>The public Maimai HydroShare database covers M8 and related Maimai catchment/hillslope phases with rainfall-runoff, water table, soil-water, isotope, tracer, and geochemical observations. Public evidence is strong for Maimai generally, though not every neighboring catchment has all variables.</t>
+          <t>The public Maimai HydroShare database covers M8 and related Maimai catchment/hillslope phases with rainfall-runoff, water table, soil-water, isotope, tracer, and geochemical observations. Public evidence is strong for Maimai generally, though not every neighboring catchment has all variables. Penna supporting match: Maimai M13; Maimai M14; Maimai M15; Maimai M5; Maimai M6; Maimai M7; Maimai M8; Maimai M9 (McGlynn et al., 2002; McGlynn et al., 2002; McDonnell etal., 2021); Penna evidence was used only for Observed flags, not public access. Official/project source override applied for public-data status.</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2790,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
+          <t>No high-confidence match</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
@@ -2802,7 +2926,7 @@
       </c>
       <c r="AR12" s="2" t="inlineStr">
         <is>
-          <t>Mahurangi papers document precipitation, flow, and soil-moisture observations used for model-structure diagnosis. CAMELS-NZ provides public hydrometeorological time series and catchment attributes, but some NZ streamflow files require provider permission; original Mahurangi soil-moisture downloads were not verified.</t>
+          <t>Mahurangi papers document precipitation, flow, and soil-moisture observations used for model-structure diagnosis. CAMELS-NZ provides public hydrometeorological time series and catchment attributes, but some NZ streamflow files require provider permission; original Mahurangi soil-moisture downloads were not verified. No high-confidence Penna catchment match found in available Part2 fuzzy matching.</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2982,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
+          <t>No high-confidence match</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr"/>
@@ -2994,7 +3118,7 @@
       </c>
       <c r="AR13" s="2" t="inlineStr">
         <is>
-          <t>WSL/EnviDat provides public long-term daily rainfall, runoff and snow measurements for Alptal, and a public EnviDat event dataset includes discharge, rainfall and deuterium in stream/rain/groundwater. WSL states sub-daily, groundwater, nutrient, isotope and other specialized data are available on request; recent Studibach publications document multi-depth soil moisture and runoff plots.</t>
+          <t>WSL/EnviDat provides public long-term daily rainfall, runoff and snow measurements for Alptal, and a public EnviDat event dataset includes discharge, rainfall and deuterium in stream/rain/groundwater. WSL states sub-daily, groundwater, nutrient, isotope and other specialized data are available on request; recent Studibach publications document multi-depth soil moisture and runoff plots. No high-confidence Penna catchment match found in available Part2 fuzzy matching. Official/project source override applied for public-data status.</t>
         </is>
       </c>
     </row>
@@ -3050,15 +3174,35 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>North river</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
-      <c r="R14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>(Perched) WT/GW dynamics and changes in GW storage</t>
+        </is>
+      </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
           <t>N</t>
@@ -3186,7 +3330,7 @@
       </c>
       <c r="AR14" s="2" t="inlineStr">
         <is>
-          <t>Publications for Stauffer, Spyhill and Triple G document precipitation/snowmelt runoff, SWE, depression ponding, soil moisture, groundwater hydraulic heads and piezometer-style monitoring of depression-focused recharge. No official downloadable original dataset was identified.</t>
+          <t>Publications for Stauffer, Spyhill and Triple G document precipitation/snowmelt runoff, SWE, depression ponding, soil moisture, groundwater hydraulic heads and piezometer-style monitoring of depression-focused recharge. No official downloadable original dataset was identified. Penna supporting match: North river (Clark et al., 2017); Penna evidence was used only for Observed flags, not public access.</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3386,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
+          <t>No high-confidence match</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
@@ -3378,7 +3522,7 @@
       </c>
       <c r="AR15" s="2" t="inlineStr">
         <is>
-          <t>Zhurucay Observatory sources describe two meteorological stations, 5-12 rain gauges, nine weirs, 38 hillslope soil-moisture sensors, water-quality/isotope monitoring and event/pre-event water isotope studies. Public downloads for full sensor time series were not verified; thesis/publication records provide partial open documentation.</t>
+          <t>Zhurucay Observatory sources describe two meteorological stations, 5-12 rain gauges, nine weirs, 38 hillslope soil-moisture sensors, water-quality/isotope monitoring and event/pre-event water isotope studies. Public downloads for full sensor time series were not verified; thesis/publication records provide partial open documentation. No high-confidence Penna catchment match found in available Part2 fuzzy matching.</t>
         </is>
       </c>
     </row>
@@ -3434,15 +3578,39 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Cofre de Perote</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Iso</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>IEOF; Lateral flow; SubFlow; Vertical flow</t>
+        </is>
+      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
           <t>N</t>
@@ -3570,7 +3738,7 @@
       </c>
       <c r="AR16" s="2" t="inlineStr">
         <is>
-          <t>Cofre de Perote/Veracruz cloud-forest studies document rainfall, streamflow, soil water/soil moisture and stable isotope observations. Searches did not identify a public official data repository for the experimental catchment time series.</t>
+          <t>Cofre de Perote/Veracruz cloud-forest studies document rainfall, streamflow, soil water/soil moisture and stable isotope observations. Searches did not identify a public official data repository for the experimental catchment time series. Penna supporting match: Cofre de Perote (Munoz-Villers et al., 2012); Penna evidence was used only for Observed flags, not public access.</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3794,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
+          <t>No high-confidence match</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
@@ -3762,7 +3930,7 @@
       </c>
       <c r="AR17" s="2" t="inlineStr">
         <is>
-          <t>Susannah Brook SB2 publication documents tipping-bucket rainfall, streamflow, shallow perched groundwater/water levels, solutes including chloride/nitrate and EC/temperature, and hillslope-riparian connectivity. WA government WIR provides free surface-water/rainfall/groundwater/water-quality access generally, but the exact SB2 experimental records were not verified.</t>
+          <t>Susannah Brook SB2 publication documents tipping-bucket rainfall, streamflow, shallow perched groundwater/water levels, solutes including chloride/nitrate and EC/temperature, and hillslope-riparian connectivity. WA government WIR provides free surface-water/rainfall/groundwater/water-quality access generally, but the exact SB2 experimental records were not verified. No high-confidence Penna catchment match found in available Part2 fuzzy matching.</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3986,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
+          <t>No high-confidence match</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
@@ -3954,7 +4122,7 @@
       </c>
       <c r="AR18" s="2" t="inlineStr">
         <is>
-          <t>J-STAGE article documents 10-minute rainfall, groundwater levels in boreholes, and volumetric soil moisture monitoring on a humid tropical forest hillslope in Sumatra. No stream discharge or public data repository was identified.</t>
+          <t>J-STAGE article documents 10-minute rainfall, groundwater levels in boreholes, and volumetric soil moisture monitoring on a humid tropical forest hillslope in Sumatra. No stream discharge or public data repository was identified. No high-confidence Penna catchment match found in available Part2 fuzzy matching.</t>
         </is>
       </c>
     </row>
@@ -4010,15 +4178,35 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Ohta EB; Hitachi Ohta FA; Hitachi Ohta FB; Hitachi Ohta ZB</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>225; 226; 227</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
       <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>S+SS; SS</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>(Perched) WT/GW dynamics and changes in GW storage; Ch. Precip; Groundwater - streamflow threshold; Lateral preferential flow; Macropore flow (no specifical vert/lat); Matrix flow; Preferential flow (no specifica vert/lat); Rainfall - streamflow threshold; Return flow/interflow; SEOF; Soil moisture- streamflow threshold; SubFlow; Water movement through bedrock or at the soil/bedrock interface (either SubFlow or GW rise)</t>
+        </is>
+      </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
           <t>Partial</t>
@@ -4031,7 +4219,7 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>https://www2.ffpri.go.jp/labs/fwdb/sites/hitachioota.htm</t>
+          <t>https://www2.ffpri.go.jp/labs/fwdb/indexE.html</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -4101,12 +4289,12 @@
       </c>
       <c r="AI19" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AJ19" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AK19" s="2" t="inlineStr">
@@ -4146,7 +4334,7 @@
       </c>
       <c r="AR19" s="2" t="inlineStr">
         <is>
-          <t>FFPRI site documents Hitachi Ohta daily precipitation and runoff records and ongoing hydrological observations; the FWDB indicates electronic files/usage terms, but Hitachi Ohta is listed as in preparation in English. Publications document hillslope soil moisture, macropore/subsurface runoff and groundwater dynamics without verified public downloads.</t>
+          <t>FFPRI site documents Hitachi Ohta daily precipitation and runoff records and ongoing hydrological observations; the FWDB indicates electronic files/usage terms, but Hitachi Ohta is listed as in preparation in English. Publications document hillslope soil moisture, macropore/subsurface runoff and groundwater dynamics without verified public downloads. Penna supporting match: Hitachi Ohta EB; Hitachi Ohta FA; Hitachi Ohta FB; Hitachi Ohta ZB (Sidle et al., 1995; 2000; 2001); Penna evidence was used only for Observed flags, not public access. Official/project source override applied for public-data status.</t>
         </is>
       </c>
     </row>
@@ -4202,15 +4390,35 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>North river</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
-      <c r="R20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>(Perched) WT/GW dynamics and changes in GW storage</t>
+        </is>
+      </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4338,7 +4546,7 @@
       </c>
       <c r="AR20" s="2" t="inlineStr">
         <is>
-          <t>Baker Creek ESSD/FRDR/Open Canada releases provide public hydrometeorological data, daily streamflow, soil moisture/temperature, snowpack/SWE and ecohydrology isotope data. Groundwater wells are documented by site descriptions; exact public groundwater time-series status is less clear, so marked partial.</t>
+          <t>Baker Creek ESSD/FRDR/Open Canada releases provide public hydrometeorological data, daily streamflow, soil moisture/temperature, snowpack/SWE and ecohydrology isotope data. Groundwater wells are documented by site descriptions; exact public groundwater time-series status is less clear, so marked partial. Penna supporting match: North river (Clark et al., 2017); Penna evidence was used only for Observed flags, not public access. Official/project source override applied for public-data status.</t>
         </is>
       </c>
     </row>
@@ -4394,15 +4602,35 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Tatsunokuchi-yama KT; Tatsunokuchi-yama MN</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>E+M</t>
+        </is>
+      </c>
       <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>S+SS</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>Lateral flow; Macropore flow (no specifical vert/lat); Pipe flow; Preferential flow (no specifica vert/lat); SubFlow; Vertical flow; Vertical preferential flow; Water movement through bedrock or at the soil/bedrock interface (either SubFlow or GW rise)</t>
+        </is>
+      </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
           <t>Partial</t>
@@ -4415,7 +4643,7 @@
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>https://www2.ffpri.go.jp/labs/fwdb/sites/tatsunokuchiyamaE.htm</t>
+          <t>https://www2.ffpri.go.jp/labs/fwdb/indexE.html</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -4530,7 +4758,7 @@
       </c>
       <c r="AR21" s="2" t="inlineStr">
         <is>
-          <t>FFPRI FWDB site documents public/terms-based daily precipitation and runoff records for Kita-dani and Minami-dani from 1937-2015. GSA/publication evidence documents soil moisture and groundwater-level monitoring in a slope/watershed, but no public download for those auxiliary observations was verified.</t>
+          <t>FFPRI FWDB site documents public/terms-based daily precipitation and runoff records for Kita-dani and Minami-dani from 1937-2015. GSA/publication evidence documents soil moisture and groundwater-level monitoring in a slope/watershed, but no public download for those auxiliary observations was verified. Penna supporting match: Tatsunokuchi-yama KT; Tatsunokuchi-yama MN (Tani et al., 1997); Penna evidence was used only for Observed flags, not public access. Official/project source override applied for public-data status.</t>
         </is>
       </c>
     </row>
@@ -4545,7 +4773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -4554,7 +4782,7 @@
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="35" customWidth="1" min="6" max="6"/>
-    <col width="90" customWidth="1" min="7" max="7"/>
+    <col width="95" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4617,7 +4845,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -4639,32 +4867,32 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Penna_Part2</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>OSTI Upper Fourmile report</t>
+          <t>Penna_globalsynthesis_DB_Part2_update_2026_01.csv</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>https://www.osti.gov/servlets/purl/1824980</t>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Rain, discharge, groundwater and hydrologic behavior</t>
+          <t>Catchment fuzzy match and runoff-process labels</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Government report describes baseline hydrological and water-quality measurements in three first-order watersheds R, B, and C.</t>
+          <t>Matched to Ranch Brook; South Creek; South Watershed; South river with process labels: (Perched) WT/GW dynamics and changes in GW storage; Return flow/interflow; SubFlow</t>
         </is>
       </c>
     </row>
@@ -4676,54 +4904,54 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Penna_Part1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>OSTI model report</t>
+          <t>Penna_globalsynthesis_DB_Part1.csv</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>https://www.osti.gov/servlets/purl/1178733</t>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Soil water/groundwater modeling and stream discharge coverage</t>
+          <t>Reference-level approach/tracer/flow type</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Report describes intensely gauged watersheds and model verification using stream discharge, meteorology and well-level data.</t>
+          <t>Reference IDs 42; 60; 178; 256; approach=E; M; tracer=; flow=S</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
+          <t>3 watersheds (R, C, B) in Upper Fourmile Branch, South Carolina, United States</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>OSTI Upper Fourmile report</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/hyp.7275</t>
+          <t>https://www.osti.gov/servlets/purl/1824980</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -4733,19 +4961,19 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Rain, discharge, groundwater and hydrologic behavior</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t>Government report describes baseline hydrological and water-quality measurements in three first-order watersheds R, B, and C.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
+          <t>3 watersheds (R, C, B) in Upper Fourmile Branch, South Carolina, United States</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -4755,12 +4983,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Brugga experimental basin summary</t>
+          <t>OSTI model report</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>https://www.hydrology.uni-freiburg.de/publika/band10-sum.html</t>
+          <t>https://www.osti.gov/servlets/purl/1178733</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -4770,12 +4998,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Tracer, precipitation, discharge, groundwater and source-area evidence</t>
+          <t>Soil water/groundwater modeling and stream discharge coverage</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>University Freiburg summary documents 18O/3H/tracer hydrograph separation, wells, runoff components and saturated areas.</t>
+          <t>Report describes intensely gauged watersheds and model verification using stream discharge, meteorology and well-level data.</t>
         </is>
       </c>
     </row>
@@ -4787,128 +5015,128 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>McMillan</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Brugga precipitation-discharge modeling paper</t>
+          <t>ProcessDatabase3-filtered.xlsx</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>https://hal.science/hal-00298620v1/document</t>
+          <t>https://doi.org/10.1002/hyp.7275</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Rain, discharge and snow-influenced hydrology</t>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Paper describes Brugga rainfall stations, discharge data and snow-influenced runoff regime.</t>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Susquehanna Shale Hills CZO - Garner Run, United States</t>
+          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Penna_Part2</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>Penna_globalsynthesis_DB_Part2_update_2026_01.csv</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.2136/vzj2018.03.0063</t>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Catchment fuzzy match and runoff-process labels</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t xml:space="preserve">Matched to Brugga with process labels: </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Susquehanna Shale Hills CZO - Garner Run, United States</t>
+          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Official_Repository</t>
+          <t>Penna_Part1</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>HydroShare Garner Run GroundHOG soil moisture</t>
+          <t>Penna_globalsynthesis_DB_Part1.csv</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>https://www.hydroshare.org/resource/4e8f26a8ac564c26b0ea2b07fca50138/</t>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Public soil moisture, soil EC and multi-depth measurements</t>
+          <t>Reference-level approach/tracer/flow type</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>HydroShare resource documents GroundHOG soil moisture, EC and temperature at 3 depths in Garner Run.</t>
+          <t>Reference IDs 82; approach=E; tracer=; flow=S</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Susquehanna Shale Hills CZO - Garner Run, United States</t>
+          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Project_Website</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Shale Hills CZO field-area datasets</t>
+          <t>Brugga experimental basin summary</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>https://czo-archive.criticalzone.org/shale-hills/data/datasets/by-field-area/</t>
+          <t>https://www.hydrology.uni-freiburg.de/publika/band10-sum.html</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -4918,34 +5146,34 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Precipitation, chemistry and groundwater support</t>
+          <t>Tracer, precipitation, discharge, groundwater and source-area evidence</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>CZO field-area listing identifies Garner Run precipitation and water/well chemistry datasets.</t>
+          <t>University Freiburg summary documents 18O/3H/tracer hydrograph separation, wells, runoff components and saturated areas.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Susquehanna Shale Hills CZO - Cole Farm, United States</t>
+          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>Brugga precipitation-discharge modeling paper</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.2136/vzj2018.03.0063</t>
+          <t>https://hal.science/hal-00298620v1/document</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -4955,34 +5183,34 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Rain, discharge and snow-influenced hydrology</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t>Paper describes Brugga rainfall stations, discharge data and snow-influenced runoff regime.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Susquehanna Shale Hills CZO - Cole Farm, United States</t>
+          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Official_Repository</t>
+          <t>Project_Website</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>HydroShare Cole Farm soil moisture</t>
+          <t>University Freiburg Brugga process page</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>https://www.hydroshare.org/resource/9ee2e7f1f0ef4746a4991a32055e6812/</t>
+          <t>http://www.hydrology.uni-freiburg.de/forsch/qbildung/d/er_chem_brugga_.htm</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -4992,34 +5220,34 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Public multi-depth soil moisture and EC</t>
+          <t>Runoff-process evidence</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>HydroShare resource documents 4-depth soil moisture, soil EC and temperature at Cole Farm.</t>
+          <t>Project page describes Brugga hillslope groundwater and runoff generation studies.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Susquehanna Shale Hills CZO - Cole Farm, United States</t>
+          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Project_Website</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Shale Hills CZO field-area datasets</t>
+          <t>Brugga fast groundwater response DOI</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>https://czo-archive.criticalzone.org/shale-hills/data/datasets/by-field-area/</t>
+          <t>https://doi.org/10.1002/hyp.5686</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -5029,34 +5257,34 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Precipitation and groundwater support</t>
+          <t>Event hydrometric/tracer evidence</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>CZO listing identifies Cole Farm precipitation and groundwater depth/temperature resources.</t>
+          <t>Publication documents wells, saturated-area discharge, deuterium, silica and ions.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Colpach, Luxembourg</t>
+          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>Brugga fast groundwater response DOI</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/hess-21-1225-2017</t>
+          <t>https://doi.org/10.1002/hyp.5686</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -5066,34 +5294,34 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Event hydrometric/tracer evidence</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t>Publication documents rapid shallow groundwater response and tracer observations in Brugga.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Colpach, Luxembourg</t>
+          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Official_Repository</t>
+          <t>Project_Website</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>GFZ/FID GEO streamflow intermittency dataset</t>
+          <t>University Freiburg Brugga process page</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5880/FIDGEO.2019.010</t>
+          <t>http://www.hydrology.uni-freiburg.de/forsch/qbildung/d/er_chem_brugga_.htm</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -5103,145 +5331,145 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Public discharge data for Colpach/Attert subcatchments</t>
+          <t>Runoff-process evidence</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>ESSD dataset reports 15-minute discharge data for Colpach among Attert subcatchments.</t>
+          <t>Project page describes Brugga hillslope groundwater and source-area runoff studies.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Colpach, Luxembourg</t>
+          <t>Susquehanna Shale Hills CZO - Garner Run, United States</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>McMillan</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Luxembourg isotope study</t>
+          <t>ProcessDatabase3-filtered.xlsx</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://hess.copernicus.org/articles/30/343/2026/</t>
+          <t>https://doi.org/10.2136/vzj2018.03.0063</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Isotope observation evidence</t>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Publication reports fortnightly precipitation and streamflow stable isotopes in nested Luxembourg catchments.</t>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Wollefsbach, Luxembourg</t>
+          <t>Susquehanna Shale Hills CZO - Garner Run, United States</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Penna_Part2</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>Penna_globalsynthesis_DB_Part2_update_2026_01.csv</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5194/hess-21-1225-2017</t>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Catchment fuzzy match and runoff-process labels</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t>Matched to Shale Hills  with process labels: (Perched) WT/GW dynamics and changes in GW storage; Groundwater - streamflow threshold; IEOF; Lateral flow; Macropore flow (no specifical vert/lat); Matrix flow; Pipe flow; Preferential flow (no specifica vert/lat); Return flow/interflow; Soil moisture -groundwater threshold; Soil moisture and rainf</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Wollefsbach, Luxembourg</t>
+          <t>Susquehanna Shale Hills CZO - Garner Run, United States</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Official_Repository</t>
+          <t>Penna_Part1</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>GFZ/FID GEO streamflow intermittency dataset</t>
+          <t>Penna_globalsynthesis_DB_Part1.csv</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5880/FIDGEO.2019.010</t>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Public discharge data for Wollefsbach/Attert subcatchments</t>
+          <t>Reference-level approach/tracer/flow type</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>ESSD dataset reports 15-minute discharge data for Wollefsbach among Attert subcatchments.</t>
+          <t>Reference IDs 49; 100; 159; 160; 216; 240; 241; approach=E; E+M; M; tracer=; flow=S; S+SS; SS</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Wollefsbach, Luxembourg</t>
+          <t>Susquehanna Shale Hills CZO - Garner Run, United States</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Official_Repository</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Luxembourg isotope study</t>
+          <t>HydroShare Garner Run GroundHOG soil moisture</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>https://hess.copernicus.org/articles/30/343/2026/</t>
+          <t>https://www.hydroshare.org/resource/4e8f26a8ac564c26b0ea2b07fca50138/</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -5251,34 +5479,34 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Isotope observation evidence</t>
+          <t>Public soil moisture, soil EC and multi-depth measurements</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Publication reports fortnightly precipitation and streamflow stable isotopes in nested Luxembourg catchments.</t>
+          <t>HydroShare resource documents GroundHOG soil moisture, EC and temperature at 3 depths in Garner Run.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Eel River CZO - Angelo, United States</t>
+          <t>Susquehanna Shale Hills CZO - Garner Run, United States</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Project_Website</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>Shale Hills CZO field-area datasets</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1029/2017WR021903</t>
+          <t>https://czo-archive.criticalzone.org/shale-hills/data/datasets/by-field-area/</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -5288,19 +5516,19 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Precipitation, chemistry and groundwater support</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t>CZO field-area listing identifies Garner Run precipitation and water/well chemistry datasets.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Eel River CZO - Angelo, United States</t>
+          <t>Susquehanna Shale Hills CZO - Garner Run, United States</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -5310,34 +5538,34 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CUAHSI HydroShare Eel CZO group</t>
+          <t>CZO Archive / CUAHSI HydroShare Shale Hills</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>https://www.hydroshare.org/group/141</t>
+          <t>https://czo-archive.criticalzone.org/shale-hills/data/datasets/</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Public Eel CZO hydrologic and chemistry resources</t>
+          <t>Official/project repository public-data status and variable availability</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>HydroShare group lists public streamflow, groundwater, soil/rock moisture, chemistry and isotope datasets.</t>
+          <t>CZO/HydroShare provides public Shale Hills hydrologic, chemistry, isotope, soil moisture, groundwater and snow-related datasets.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Eel River CZO - Angelo, United States</t>
+          <t>Susquehanna Shale Hills CZO - Garner Run, United States</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -5347,34 +5575,34 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Eel CZO Angelo isotope HydroShare</t>
+          <t>CUAHSI HydroShare Shale Hills CZO - Garner Run</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>https://www.hydroshare.org/resource/bbe40682aa8644b882df84c5db3938fa/</t>
+          <t>https://www.hydroshare.org/resource/4e8f26a8ac564c26b0ea2b07fca50138/</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Stable isotopes from rainfall, streams, wells and soils</t>
+          <t>Official/project repository public-data status and variable availability</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>HydroShare resource documents stable isotope analyses from rain, streams, wells, soil and stem water.</t>
+          <t>HydroShare Garner Run GroundHOG data include multi-depth soil moisture and soil EC; CZO records describe precipitation and water chemistry resources.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Eel River CZO - Sagehorn, United States</t>
+          <t>Susquehanna Shale Hills CZO - Cole Farm, United States</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -5389,12 +5617,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1029/2017WR021903</t>
+          <t>https://doi.org/10.2136/vzj2018.03.0063</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5411,81 +5639,81 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Eel River CZO - Sagehorn, United States</t>
+          <t>Susquehanna Shale Hills CZO - Cole Farm, United States</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Project_Website</t>
+          <t>Penna_Part2</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Eel CZO field-area datasets</t>
+          <t>Penna_globalsynthesis_DB_Part2_update_2026_01.csv</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>https://czo-archive.criticalzone.org/eel/data/datasets/by-field-area/</t>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Project monitoring evidence for Sagehorn</t>
+          <t>Catchment fuzzy match and runoff-process labels</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>CZO Archive describes Sagehorn-Russell Ranch with a weather station and monitored wells, but direct downloads were not verified.</t>
+          <t>Matched to Shale Hills  with process labels: (Perched) WT/GW dynamics and changes in GW storage; Groundwater - streamflow threshold; IEOF; Lateral flow; Macropore flow (no specifical vert/lat); Matrix flow; Pipe flow; Preferential flow (no specifica vert/lat); Return flow/interflow; Soil moisture -groundwater threshold; Soil moisture and rainf</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Maimai M8 experimental catchment, New Zealand</t>
+          <t>Susquehanna Shale Hills CZO - Cole Farm, United States</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Penna_Part1</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>Penna_globalsynthesis_DB_Part1.csv</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1029/wr026i011p02821</t>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Reference-level approach/tracer/flow type</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t>Reference IDs 49; 100; 159; 160; 216; 240; 241; approach=E; E+M; M; tracer=; flow=S; S+SS; SS</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Maimai M8 experimental catchment, New Zealand</t>
+          <t>Susquehanna Shale Hills CZO - Cole Farm, United States</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -5495,12 +5723,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Maimai HydroShare repository</t>
+          <t>HydroShare Cole Farm soil moisture</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>https://www.hydroshare.org/resource/a292cb65a5d24a31a60978b2ab390266/</t>
+          <t>https://www.hydroshare.org/resource/9ee2e7f1f0ef4746a4991a32055e6812/</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -5510,34 +5738,34 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Public Maimai M8 rainfall-runoff, isotope, groundwater and soil-water data</t>
+          <t>Public multi-depth soil moisture and EC</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>HydroShare database contains public Maimai observations from multiple research phases.</t>
+          <t>HydroShare resource documents 4-depth soil moisture, soil EC and temperature at Cole Farm.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Maimai catchments, New Zealand</t>
+          <t>Susquehanna Shale Hills CZO - Cole Farm, United States</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Project_Website</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>Shale Hills CZO field-area datasets</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/s0022-1694(01)00559-5</t>
+          <t>https://czo-archive.criticalzone.org/shale-hills/data/datasets/by-field-area/</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -5547,19 +5775,19 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Precipitation and groundwater support</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t>CZO listing identifies Cole Farm precipitation and groundwater depth/temperature resources.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Maimai catchments, New Zealand</t>
+          <t>Susquehanna Shale Hills CZO - Cole Farm, United States</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -5569,123 +5797,123 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Maimai HydroShare repository</t>
+          <t>CZO Archive / CUAHSI HydroShare Shale Hills</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>https://www.hydroshare.org/resource/a292cb65a5d24a31a60978b2ab390266/</t>
+          <t>https://czo-archive.criticalzone.org/shale-hills/data/datasets/</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Public Maimai catchment observations</t>
+          <t>Official/project repository public-data status and variable availability</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>HydroShare database contains rainfall-runoff, isotope, water-table, soil-water and tracer observations for Maimai studies.</t>
+          <t>CZO/HydroShare provides public Shale Hills hydrologic, chemistry, isotope, soil moisture, groundwater and snow-related datasets.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Mahurangi catchments, New Zealand</t>
+          <t>Susquehanna Shale Hills CZO - Cole Farm, United States</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Official_Repository</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>CUAHSI HydroShare Shale Hills CZO - Cole Farm</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/hyp.7841</t>
+          <t>https://www.hydroshare.org/resource/9ee2e7f1f0ef4746a4991a32055e6812/</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Official/project repository public-data status and variable availability</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t>HydroShare Cole Farm GroundHOG data include 4-depth soil moisture and soil EC; CZO records describe precipitation and groundwater resources.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Mahurangi catchments, New Zealand</t>
+          <t>Colpach, Luxembourg</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Official_Repository</t>
+          <t>McMillan</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>CAMELS-NZ dataset DOI</t>
+          <t>ProcessDatabase3-filtered.xlsx</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.26021/canterburynz.28827644</t>
+          <t>https://doi.org/10.5194/hess-21-1225-2017</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Public/permissioned hydrometeorological data</t>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>CAMELS-NZ provides hourly hydrometeorological time series and catchment attributes; some streamflow requires permission.</t>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Mahurangi catchments, New Zealand</t>
+          <t>Colpach, Luxembourg</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Official_Repository</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Mahurangi model-diagnostics paper</t>
+          <t>GFZ/FID GEO streamflow intermittency dataset</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/hyp.7841</t>
+          <t>https://doi.org/10.5880/FIDGEO.2019.010</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -5695,34 +5923,34 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Rain, streamflow and soil-moisture observation evidence</t>
+          <t>Public discharge data for Colpach/Attert subcatchments</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Publication documents use of precipitation, flow and soil moisture data for Mahurangi process diagnosis.</t>
+          <t>ESSD dataset reports 15-minute discharge data for Colpach among Attert subcatchments.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Alptal watershed, Switzerland</t>
+          <t>Colpach, Luxembourg</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>Luxembourg isotope study</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>https://publicaciones.unirioja.es/ojs/index.php/cig/article/viewFile/3349/3083</t>
+          <t>https://hess.copernicus.org/articles/30/343/2026/</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -5732,19 +5960,19 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Isotope observation evidence</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t>Publication reports fortnightly precipitation and streamflow stable isotopes in nested Luxembourg catchments.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Alptal watershed, Switzerland</t>
+          <t>Colpach, Luxembourg</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -5754,86 +5982,86 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>WSL EnviDat Alptal observatory</t>
+          <t>GFZ/FID GEO / Luxembourg hydrometric datasets</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>https://www.envidat.ch/dataset/longterm-hydrological-observatory-alptal-central-switzerland</t>
+          <t>https://doi.org/10.5880/FIDGEO.2019.010</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Public rainfall, runoff and snow data</t>
+          <t>Official/project repository public-data status and variable availability</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>EnviDat provides public long-term daily hydrometeorological and snow measurements.</t>
+          <t>Luxembourg/Attert datasets provide public discharge/hydrometeorological data; isotope studies support precipitation and stream-water isotope observations for nested catchments.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Alptal watershed, Switzerland</t>
+          <t>Wollefsbach, Luxembourg</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Official_Repository</t>
+          <t>McMillan</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Alptal event isotope dataset</t>
+          <t>ProcessDatabase3-filtered.xlsx</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>https://envidat.ch/metadata/streamwater-level-and-isotopic-composition-four-rainfall-events-studibach</t>
+          <t>https://doi.org/10.5194/hess-21-1225-2017</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Public event rainfall, discharge, groundwater isotope data</t>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>EnviDat dataset contains discharge, rainfall and deuterium compositions of streamwater, rainwater and groundwater.</t>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Alptal watershed, Switzerland</t>
+          <t>Wollefsbach, Luxembourg</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Project_Website</t>
+          <t>Official_Repository</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>WSL Alptal data page</t>
+          <t>GFZ/FID GEO streamflow intermittency dataset</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>https://www.wsl.ch/en/about-wsl/instrumented-field-sites-and-laboratories/experimented-field-sites-for-natural-hazards/torrent-investigation-in-the-alptal/data/</t>
+          <t>https://doi.org/10.5880/FIDGEO.2019.010</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -5843,34 +6071,34 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Request/partial data access evidence</t>
+          <t>Public discharge data for Wollefsbach/Attert subcatchments</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>WSL states sub-daily, groundwater, isotope and specialized data are available by request.</t>
+          <t>ESSD dataset reports 15-minute discharge data for Wollefsbach among Attert subcatchments.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Triple G, Spyhill, and Stauffer Catchments, Northern Prairie Region, Canada</t>
+          <t>Wollefsbach, Luxembourg</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>Luxembourg isotope study</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/hyp.14277</t>
+          <t>https://hess.copernicus.org/articles/30/343/2026/</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -5880,34 +6108,34 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Isotope observation evidence</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t>Publication reports fortnightly precipitation and streamflow stable isotopes in nested Luxembourg catchments.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Triple G, Spyhill, and Stauffer Catchments, Northern Prairie Region, Canada</t>
+          <t>Wollefsbach, Luxembourg</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Official_Repository</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>HESS frozen-soil recharge paper</t>
+          <t>GFZ/FID GEO streamflow intermittency dataset</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>https://hess.copernicus.org/articles/23/5017/2019/</t>
+          <t>https://doi.org/10.5880/FIDGEO.2019.010</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -5917,19 +6145,19 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Snow, runoff, soil moisture and groundwater observations</t>
+          <t>Public Wollefsbach discharge</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Publication documents SWE, ponding, soil moisture and hydraulic-head monitoring at Triple G, Spyhill and Stauffer.</t>
+          <t>Dataset includes discharge for Wollefsbach among Attert subcatchments.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Triple G, Spyhill, and Stauffer Catchments, Northern Prairie Region, Canada</t>
+          <t>Wollefsbach, Luxembourg</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -5939,12 +6167,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>HESS midwinter melts paper</t>
+          <t>Luxembourg isotope study</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>https://hess.copernicus.org/articles/23/1867/2019/</t>
+          <t>https://hess.copernicus.org/articles/30/343/2026/</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -5954,108 +6182,108 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Event runoff and groundwater response evidence</t>
+          <t>Isotope support</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Publication documents ponded snowmelt runoff and groundwater recharge responses.</t>
+          <t>Publication reports precipitation and streamflow isotopes for nested Luxembourg catchments.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Zhurucay River Ecohydrological Observatory, Andean cordillera, Ecuador</t>
+          <t>Wollefsbach, Luxembourg</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Official_Repository</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>GFZ/FID GEO / Luxembourg hydrometric datasets</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/hyp.10927</t>
+          <t>https://doi.org/10.5880/FIDGEO.2019.010</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Official/project repository public-data status and variable availability</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t>Luxembourg/Attert datasets provide public discharge/hydrometeorological data; isotope studies support precipitation and stream-water isotope observations for nested catchments.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Zhurucay River Ecohydrological Observatory, Andean cordillera, Ecuador</t>
+          <t>Eel River CZO - Angelo, United States</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Project_Website</t>
+          <t>McMillan</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>University of Cuenca Zhurucay Observatory</t>
+          <t>ProcessDatabase3-filtered.xlsx</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>https://www.ucuenca.edu.ec/idrhica/index.php/en/laboratories-and-observatories/zhurucay-ecohydrological-observatory/</t>
+          <t>https://doi.org/10.1029/2017WR021903</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Project monitoring evidence</t>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Referenced observatory page is cited by publications for Zhurucay instrumentation.</t>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Zhurucay River Ecohydrological Observatory, Andean cordillera, Ecuador</t>
+          <t>Eel River CZO - Angelo, United States</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Official_Repository</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Frontiers Zhurucay simulation paper</t>
+          <t>CUAHSI HydroShare Eel CZO group</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>https://www.frontiersin.org/journals/environmental-science/articles/10.3389/fenvs.2024.1303388/full</t>
+          <t>https://www.hydroshare.org/group/141</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -6065,34 +6293,34 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Rain, streamflow and soil-moisture observations</t>
+          <t>Public Eel CZO hydrologic and chemistry resources</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Paper describes rain gauges, weirs and 38 soil moisture sensors.</t>
+          <t>HydroShare group lists public streamflow, groundwater, soil/rock moisture, chemistry and isotope datasets.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Zhurucay River Ecohydrological Observatory, Andean cordillera, Ecuador</t>
+          <t>Eel River CZO - Angelo, United States</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Official_Repository</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>USGS publication page for Zhurucay isotope paper</t>
+          <t>Eel CZO Angelo isotope HydroShare</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>https://pubs.usgs.gov/publication/70171508</t>
+          <t>https://www.hydroshare.org/resource/bbe40682aa8644b882df84c5db3938fa/</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -6102,19 +6330,19 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Isotope and hydrometric observation evidence</t>
+          <t>Stable isotopes from rainfall, streams, wells and soils</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>USGS record documents combined isotopic and hydrometric study at Zhurucay.</t>
+          <t>HydroShare resource documents stable isotope analyses from rain, streams, wells, soil and stem water.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>A catchment in Cofre de Perote volcano, Mexico</t>
+          <t>Eel River CZO - Sagehorn, United States</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -6129,12 +6357,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1029/2011wr011316</t>
+          <t>https://doi.org/10.1029/2017WR021903</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -6151,22 +6379,22 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>A catchment in Cofre de Perote volcano, Mexico</t>
+          <t>Eel River CZO - Sagehorn, United States</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Project_Website</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Cofre de Perote isotope ecohydrology paper</t>
+          <t>Eel CZO field-area datasets</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1029/2011WR011316</t>
+          <t>https://czo-archive.criticalzone.org/eel/data/datasets/by-field-area/</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -6176,130 +6404,130 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Stable isotope, soil water and stream evidence</t>
+          <t>Project monitoring evidence for Sagehorn</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Publication reports dual stable isotopes in precipitation, soil water, plant water and streams.</t>
+          <t>CZO Archive describes Sagehorn-Russell Ranch with a weather station and monitored wells, but direct downloads were not verified.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>A catchment in Cofre de Perote volcano, Mexico</t>
+          <t>Maimai M8 experimental catchment, New Zealand</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>McMillan</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Veracruz rainfall-runoff response paper</t>
+          <t>ProcessDatabase3-filtered.xlsx</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/hyp.13800</t>
+          <t>https://doi.org/10.1029/wr026i011p02821</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>High-resolution rainfall and streamflow evidence</t>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Publication documents 4-year 10-minute rainfall and streamflow observations in headwater microcatchments.</t>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>SB2 subcatchment, Susannah Brook, Western Australia, Australia</t>
+          <t>Maimai M8 experimental catchment, New Zealand</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Penna_Part2</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>Penna_globalsynthesis_DB_Part2_update_2026_01.csv</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.advwatres.2005.02.014</t>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Catchment fuzzy match and runoff-process labels</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t xml:space="preserve">Matched to Maimai M8; Maimai M13; Maimai M14; Maimai M15; Maimai M5; Maimai M6; Maimai M7; Maimai M9 with process labels: (Perched) WT/GW dynamics and changes in GW storage; Dynamics of saturated areas; Groundwater - streamflow threshold; Lateral flow; Matrix flow; Pipe flow; Preferential flow (no specifica vert/lat); SEOF; Soil moisture-subsurface flow threshold; SubFlow; Vertical flow; Water movement through bedrock </t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>SB2 subcatchment, Susannah Brook, Western Australia, Australia</t>
+          <t>Maimai M8 experimental catchment, New Zealand</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Penna_Part1</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Susannah Brook SB2 publication</t>
+          <t>Penna_globalsynthesis_DB_Part1.csv</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/abs/pii/S0022169406003234</t>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Rainfall, runoff, groundwater, EC and connectivity observations</t>
+          <t>Reference-level approach/tracer/flow type</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Publication documents tipping-bucket rainfall, streamflow, shallow perched groundwater and EC/solute observations.</t>
+          <t>Reference IDs 169; 170; approach=E+M; tracer=Iso+Ions+EC+Dyes; flow=S+SS</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>SB2 subcatchment, Susannah Brook, Western Australia, Australia</t>
+          <t>Maimai M8 experimental catchment, New Zealand</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -6309,86 +6537,86 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Western Australia surface water data page</t>
+          <t>Maimai HydroShare repository</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>https://www.wa.gov.au/service/natural-resources/water-resources/surface-water</t>
+          <t>https://www.hydroshare.org/resource/a292cb65a5d24a31a60978b2ab390266/</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Official monitoring portal evidence</t>
+          <t>Observation/public-data decision support</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>WA government states free online WIR access for streamflow, rainfall, groundwater and water-quality data.</t>
+          <t>HydroShare repository contains public Maimai M8 rainfall-runoff, isotope, soil-water, water-table, trench-flow, tracer, and geochemistry data.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Sumatra, Indonesia</t>
+          <t>Maimai M8 experimental catchment, New Zealand</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>Maimai database publication DOI</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3178/hrl.15.23</t>
+          <t>https://doi.org/10.1002/hyp.14112</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Observation/public-data decision support</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t>Data paper confirms Maimai M8 database is publicly available on HydroShare.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Sumatra, Indonesia</t>
+          <t>Maimai M8 experimental catchment, New Zealand</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Official_Repository</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>J-STAGE Sumatra hillslope paper</t>
+          <t>Maimai HydroShare repository</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>https://www.jstage.jst.go.jp/article/hrl/15/2/15_23/_article/-char/ja/</t>
+          <t>https://www.hydroshare.org/resource/a292cb65a5d24a31a60978b2ab390266/</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -6398,182 +6626,182 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Rainfall, soil moisture and groundwater observations</t>
+          <t>Public Maimai M8 rainfall-runoff, isotope, groundwater and soil-water data</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Open publication documents 10-minute rainfall, soil moisture and groundwater monitoring on the Sumatra hillslope.</t>
+          <t>HydroShare database contains public Maimai observations from multiple research phases.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Hitachi Ohta Experimental Watershed, Japan</t>
+          <t>Maimai M8 experimental catchment, New Zealand</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Official_Repository</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>CUAHSI HydroShare Maimai Experimental Watershed</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/(SICI)1099-1085(20000228)14:3%3C369::AID-HYP943%3E3.0.CO;2-P</t>
+          <t>https://www.hydroshare.org/resource/a292cb65a5d24a31a60978b2ab390266/</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Official/project repository public-data status and variable availability</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t>Public Maimai HydroShare database includes rainfall-runoff, isotopes, soil-water/matric potential, water-table/well, trench-flow/tracer and geochemical data.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Hitachi Ohta Experimental Watershed, Japan</t>
+          <t>Maimai catchments, New Zealand</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Official_Repository</t>
+          <t>McMillan</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>FFPRI Hitachi Ohta site</t>
+          <t>ProcessDatabase3-filtered.xlsx</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>https://www2.ffpri.go.jp/labs/fwdb/sites/hitachioota.htm</t>
+          <t>https://doi.org/10.1016/s0022-1694(01)00559-5</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Precipitation and runoff data record</t>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>FFPRI page lists daily precipitation and daily runoff periods and watershed metadata.</t>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Hitachi Ohta Experimental Watershed, Japan</t>
+          <t>Maimai catchments, New Zealand</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Official_Repository</t>
+          <t>Penna_Part2</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>FFPRI FWDB English page</t>
+          <t>Penna_globalsynthesis_DB_Part2_update_2026_01.csv</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>https://www2.ffpri.go.jp/labs/fwdb/indexE.html</t>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Official database access context</t>
+          <t>Catchment fuzzy match and runoff-process labels</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>FWDB page states published forest watershed observations are provided as electronic files and lists Hitachi Ohta in preparation.</t>
+          <t xml:space="preserve">Matched to Maimai M13; Maimai M14; Maimai M15; Maimai M5; Maimai M6; Maimai M7; Maimai M8; Maimai M9 with process labels: (Perched) WT/GW dynamics and changes in GW storage; Dynamics of saturated areas; Groundwater - streamflow threshold; Lateral flow; Matrix flow; Pipe flow; Preferential flow (no specifica vert/lat); SEOF; Soil moisture-subsurface flow threshold; SubFlow; Vertical flow; Water movement through bedrock </t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Hitachi Ohta Experimental Watershed, Japan</t>
+          <t>Maimai catchments, New Zealand</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Penna_Part1</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Hitachi Ohta subsurface runoff paper</t>
+          <t>Penna_globalsynthesis_DB_Part1.csv</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/hyp.278</t>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Soil moisture/groundwater/process observations</t>
+          <t>Reference-level approach/tracer/flow type</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Publication confirms subsurface runoff and hillslope soil-profile observations.</t>
+          <t>Reference IDs 169; 170; approach=E+M; tracer=Iso+Ions+EC+Dyes; flow=S+SS</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Baker Creek watershed, Yellowknife Northwest Territories, Canada</t>
+          <t>Maimai catchments, New Zealand</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Official_Repository</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>Maimai HydroShare repository</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/2014JG002809</t>
+          <t>https://www.hydroshare.org/resource/a292cb65a5d24a31a60978b2ab390266/</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -6583,19 +6811,19 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Public Maimai catchment observations</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t>HydroShare database contains rainfall-runoff, isotope, water-table, soil-water and tracer observations for Maimai studies.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Baker Creek watershed, Yellowknife Northwest Territories, Canada</t>
+          <t>Maimai catchments, New Zealand</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -6605,86 +6833,86 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Baker Creek FRDR data release</t>
+          <t>CUAHSI HydroShare Maimai Experimental Watershed</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.20383/101.026</t>
+          <t>https://www.hydroshare.org/resource/a292cb65a5d24a31a60978b2ab390266/</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Public hydrometeorological, streamflow, soil moisture and snow data</t>
+          <t>Official/project repository public-data status and variable availability</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>ESSD data paper states Baker Creek data are publicly available via FRDR.</t>
+          <t>Public Maimai HydroShare database includes rainfall-runoff, isotopes, soil-water/matric potential, water-table/well, trench-flow/tracer and geochemical data.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Baker Creek watershed, Yellowknife Northwest Territories, Canada</t>
+          <t>Mahurangi catchments, New Zealand</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Official_Repository</t>
+          <t>McMillan</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Open Canada Baker Creek Ecohydrology Data</t>
+          <t>ProcessDatabase3-filtered.xlsx</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>https://open.canada.ca/data/en/dataset/235f97ec-6195-44be-85a5-ae5e254026ee</t>
+          <t>https://doi.org/10.1002/hyp.7841</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Public isotope and soil moisture ecohydrology data</t>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Open Canada dataset includes meteorological, eddy covariance, stable isotope, soil temperature and soil moisture data.</t>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Baker Creek watershed, Yellowknife Northwest Territories, Canada</t>
+          <t>Mahurangi catchments, New Zealand</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Project_Website</t>
+          <t>Official_Repository</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Nordata Baker Creek site description</t>
+          <t>CAMELS-NZ dataset DOI</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://nordata.physics.utoronto.ca/en/annexes-datasets-descriptions/75-snow/baker-creek-research-site-nwt/</t>
+          <t>https://doi.org/10.26021/canterburynz.28827644</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -6694,34 +6922,34 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Groundwater and snow monitoring evidence</t>
+          <t>Public/permissioned hydrometeorological data</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Site description documents instruments, groundwater wells, soil moisture and snow surveys.</t>
+          <t>CAMELS-NZ provides hourly hydrometeorological time series and catchment attributes; some streamflow requires permission.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Tatsunokuchi-yama Experimental Forest, Japan</t>
+          <t>Mahurangi catchments, New Zealand</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>Mahurangi model-diagnostics paper</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/S0022-1694(97)00018-8</t>
+          <t>https://doi.org/10.1002/hyp.7841</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -6731,56 +6959,56 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Rain, streamflow and soil-moisture observation evidence</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t>Publication documents use of precipitation, flow and soil moisture data for Mahurangi process diagnosis.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Tatsunokuchi-yama Experimental Forest, Japan</t>
+          <t>Alptal watershed, Switzerland</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Official_Repository</t>
+          <t>McMillan</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>FFPRI Tatsunokuchi-yama site</t>
+          <t>ProcessDatabase3-filtered.xlsx</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>https://www2.ffpri.go.jp/labs/fwdb/sites/tatsunokuchiyamaE.htm</t>
+          <t>https://publicaciones.unirioja.es/ojs/index.php/cig/article/viewFile/3349/3083</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Precipitation and runoff data record</t>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>FFPRI page lists daily precipitation and daily runoff records for Kita-dani and Minami-dani.</t>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Tatsunokuchi-yama Experimental Forest, Japan</t>
+          <t>Alptal watershed, Switzerland</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -6790,12 +7018,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>FFPRI FWDB English page</t>
+          <t>WSL EnviDat Alptal observatory</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>https://www2.ffpri.go.jp/labs/fwdb/indexE.html</t>
+          <t>https://www.envidat.ch/dataset/longterm-hydrological-observatory-alptal-central-switzerland</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -6805,49 +7033,1603 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Official database access context</t>
+          <t>Public rainfall, runoff and snow data</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>FWDB page states forest watershed observations are provided as electronic files.</t>
+          <t>EnviDat provides public long-term daily hydrometeorological and snow measurements.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>Alptal watershed, Switzerland</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Official_Repository</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Alptal event isotope dataset</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>https://envidat.ch/metadata/streamwater-level-and-isotopic-composition-four-rainfall-events-studibach</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Public event rainfall, discharge, groundwater isotope data</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>EnviDat dataset contains discharge, rainfall and deuterium compositions of streamwater, rainwater and groundwater.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Alptal watershed, Switzerland</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Project_Website</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>WSL Alptal data page</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wsl.ch/en/about-wsl/instrumented-field-sites-and-laboratories/experimented-field-sites-for-natural-hazards/torrent-investigation-in-the-alptal/data/</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Request/partial data access evidence</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>WSL states sub-daily, groundwater, isotope and specialized data are available by request.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Alptal watershed, Switzerland</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Official_Repository</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>WSL EnviDat Alptal observatory</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.envidat.ch/dataset/longterm-hydrological-observatory-alptal-central-switzerland</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Official/project repository public-data status and variable availability</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>WSL/EnviDat provides public long-term rainfall/runoff/snow and event isotope data; sub-daily and specialized groundwater/soil data are partly request-mediated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Triple G, Spyhill, and Stauffer Catchments, Northern Prairie Region, Canada</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>McMillan</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>ProcessDatabase3-filtered.xlsx</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/hyp.14277</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Triple G, Spyhill, and Stauffer Catchments, Northern Prairie Region, Canada</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Penna_Part2</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Penna_globalsynthesis_DB_Part2_update_2026_01.csv</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Catchment fuzzy match and runoff-process labels</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Matched to North river with process labels: (Perched) WT/GW dynamics and changes in GW storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Triple G, Spyhill, and Stauffer Catchments, Northern Prairie Region, Canada</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Penna_Part1</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Penna_globalsynthesis_DB_Part1.csv</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Reference-level approach/tracer/flow type</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Reference IDs 42; approach=M; tracer=; flow=S</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Triple G, Spyhill, and Stauffer Catchments, Northern Prairie Region, Canada</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>HESS frozen-soil recharge paper</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>https://hess.copernicus.org/articles/23/5017/2019/</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Snow, runoff, soil moisture and groundwater observations</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Publication documents SWE, ponding, soil moisture and hydraulic-head monitoring at Triple G, Spyhill and Stauffer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Triple G, Spyhill, and Stauffer Catchments, Northern Prairie Region, Canada</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>HESS midwinter melts paper</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>https://hess.copernicus.org/articles/23/1867/2019/</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Event runoff and groundwater response evidence</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Publication documents ponded snowmelt runoff and groundwater recharge responses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Zhurucay River Ecohydrological Observatory, Andean cordillera, Ecuador</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>McMillan</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>ProcessDatabase3-filtered.xlsx</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/hyp.10927</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Zhurucay River Ecohydrological Observatory, Andean cordillera, Ecuador</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Project_Website</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>University of Cuenca Zhurucay Observatory</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ucuenca.edu.ec/idrhica/index.php/en/laboratories-and-observatories/zhurucay-ecohydrological-observatory/</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Project monitoring evidence</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Referenced observatory page is cited by publications for Zhurucay instrumentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Zhurucay River Ecohydrological Observatory, Andean cordillera, Ecuador</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Frontiers Zhurucay simulation paper</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.frontiersin.org/journals/environmental-science/articles/10.3389/fenvs.2024.1303388/full</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Rain, streamflow and soil-moisture observations</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Paper describes rain gauges, weirs and 38 soil moisture sensors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Zhurucay River Ecohydrological Observatory, Andean cordillera, Ecuador</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>USGS publication page for Zhurucay isotope paper</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>https://pubs.usgs.gov/publication/70171508</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Isotope and hydrometric observation evidence</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>USGS record documents combined isotopic and hydrometric study at Zhurucay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>A catchment in Cofre de Perote volcano, Mexico</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>McMillan</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>ProcessDatabase3-filtered.xlsx</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1029/2011wr011316</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>A catchment in Cofre de Perote volcano, Mexico</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Penna_Part2</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Penna_globalsynthesis_DB_Part2_update_2026_01.csv</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Catchment fuzzy match and runoff-process labels</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Matched to Cofre de Perote with process labels: IEOF; Lateral flow; SubFlow; Vertical flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>A catchment in Cofre de Perote volcano, Mexico</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Penna_Part1</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Penna_globalsynthesis_DB_Part1.csv</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Reference-level approach/tracer/flow type</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Reference IDs 181; approach=E; tracer=Iso; flow=S</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>A catchment in Cofre de Perote volcano, Mexico</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Cofre de Perote isotope ecohydrology paper</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1029/2011WR011316</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Stable isotope, soil water and stream evidence</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Publication reports dual stable isotopes in precipitation, soil water, plant water and streams.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>A catchment in Cofre de Perote volcano, Mexico</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Veracruz rainfall-runoff response paper</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/hyp.13800</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>High-resolution rainfall and streamflow evidence</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Publication documents 4-year 10-minute rainfall and streamflow observations in headwater microcatchments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>SB2 subcatchment, Susannah Brook, Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>McMillan</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>ProcessDatabase3-filtered.xlsx</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.advwatres.2005.02.014</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>SB2 subcatchment, Susannah Brook, Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Susannah Brook SB2 publication</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0022169406003234</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Rainfall, runoff, groundwater, EC and connectivity observations</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Publication documents tipping-bucket rainfall, streamflow, shallow perched groundwater and EC/solute observations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>SB2 subcatchment, Susannah Brook, Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Official_Repository</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Western Australia surface water data page</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wa.gov.au/service/natural-resources/water-resources/surface-water</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Official monitoring portal evidence</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>WA government states free online WIR access for streamflow, rainfall, groundwater and water-quality data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Sumatra, Indonesia</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>McMillan</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>ProcessDatabase3-filtered.xlsx</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3178/hrl.15.23</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Sumatra, Indonesia</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>J-STAGE Sumatra hillslope paper</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jstage.jst.go.jp/article/hrl/15/2/15_23/_article/-char/ja/</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Rainfall, soil moisture and groundwater observations</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Open publication documents 10-minute rainfall, soil moisture and groundwater monitoring on the Sumatra hillslope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Ohta Experimental Watershed, Japan</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>McMillan</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>ProcessDatabase3-filtered.xlsx</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/(SICI)1099-1085(20000228)14:3%3C369::AID-HYP943%3E3.0.CO;2-P</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Ohta Experimental Watershed, Japan</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Penna_Part2</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Penna_globalsynthesis_DB_Part2_update_2026_01.csv</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Catchment fuzzy match and runoff-process labels</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Matched to Hitachi Ohta EB; Hitachi Ohta FA; Hitachi Ohta FB; Hitachi Ohta ZB with process labels: (Perched) WT/GW dynamics and changes in GW storage; Ch. Precip; Groundwater - streamflow threshold; Lateral preferential flow; Macropore flow (no specifical vert/lat); Matrix flow; Preferential flow (no specifica vert/lat); Rainfall - streamflow threshold; Return flow/interflow; SEOF; Soil moisture-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Ohta Experimental Watershed, Japan</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Penna_Part1</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Penna_globalsynthesis_DB_Part1.csv</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Reference-level approach/tracer/flow type</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Reference IDs 225; 226; 227; approach=E; tracer=; flow=S+SS; SS</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Ohta Experimental Watershed, Japan</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Official_Repository</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>FFPRI Hitachi Ohta site</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>https://www2.ffpri.go.jp/labs/fwdb/sites/hitachioota.htm</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Precipitation and runoff data record</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>FFPRI page lists daily precipitation and daily runoff periods and watershed metadata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Ohta Experimental Watershed, Japan</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Official_Repository</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>FFPRI FWDB English page</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>https://www2.ffpri.go.jp/labs/fwdb/indexE.html</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Official database access context</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>FWDB page states published forest watershed observations are provided as electronic files and lists Hitachi Ohta in preparation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Ohta Experimental Watershed, Japan</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Ohta subsurface runoff paper</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/hyp.278</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Soil moisture/groundwater/process observations</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Publication confirms subsurface runoff and hillslope soil-profile observations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Ohta Experimental Watershed, Japan</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Official_Repository</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>FFPRI Forest Experimental Watershed Database</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>https://www2.ffpri.go.jp/labs/fwdb/indexE.html</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Official/project repository public-data status and variable availability</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>FFPRI FWDB documents daily precipitation and runoff records for Japanese experimental watersheds; auxiliary soil/groundwater observations are publication-supported but not verified as public.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Baker Creek watershed, Yellowknife Northwest Territories, Canada</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>McMillan</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>ProcessDatabase3-filtered.xlsx</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/2014JG002809</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Baker Creek watershed, Yellowknife Northwest Territories, Canada</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Penna_Part2</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Penna_globalsynthesis_DB_Part2_update_2026_01.csv</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Catchment fuzzy match and runoff-process labels</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Matched to North river with process labels: (Perched) WT/GW dynamics and changes in GW storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Baker Creek watershed, Yellowknife Northwest Territories, Canada</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Penna_Part1</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Penna_globalsynthesis_DB_Part1.csv</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Reference-level approach/tracer/flow type</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Reference IDs 42; approach=M; tracer=; flow=S</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Baker Creek watershed, Yellowknife Northwest Territories, Canada</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Official_Repository</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Baker Creek FRDR data release</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.20383/101.026</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Public hydrometeorological, streamflow, soil moisture and snow data</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>ESSD data paper states Baker Creek data are publicly available via FRDR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Baker Creek watershed, Yellowknife Northwest Territories, Canada</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Official_Repository</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Open Canada Baker Creek Ecohydrology Data</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>https://open.canada.ca/data/en/dataset/235f97ec-6195-44be-85a5-ae5e254026ee</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Public isotope and soil moisture ecohydrology data</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Open Canada dataset includes meteorological, eddy covariance, stable isotope, soil temperature and soil moisture data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Baker Creek watershed, Yellowknife Northwest Territories, Canada</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Project_Website</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Nordata Baker Creek site description</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>https://nordata.physics.utoronto.ca/en/annexes-datasets-descriptions/75-snow/baker-creek-research-site-nwt/</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Groundwater and snow monitoring evidence</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Site description documents instruments, groundwater wells, soil moisture and snow surveys.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Baker Creek watershed, Yellowknife Northwest Territories, Canada</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Official_Repository</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>FRDR / Open Government Canada Baker Creek Research Watershed</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.20383/101.026</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Official/project repository public-data status and variable availability</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Baker Creek public data releases include hydrometeorology, streamflow, soil moisture/temperature, snowpack/SWE and ecohydrology isotope data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
           <t>Tatsunokuchi-yama Experimental Forest, Japan</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>McMillan</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>ProcessDatabase3-filtered.xlsx</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/S0022-1694(97)00018-8</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Tatsunokuchi-yama Experimental Forest, Japan</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Penna_Part2</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Penna_globalsynthesis_DB_Part2_update_2026_01.csv</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Catchment fuzzy match and runoff-process labels</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Matched to Tatsunokuchi-yama KT; Tatsunokuchi-yama MN with process labels: Lateral flow; Macropore flow (no specifical vert/lat); Pipe flow; Preferential flow (no specifica vert/lat); SubFlow; Vertical flow; Vertical preferential flow; Water movement through bedrock or at the soil/bedrock interface (either SubFlow or GW rise)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Tatsunokuchi-yama Experimental Forest, Japan</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Penna_Part1</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Penna_globalsynthesis_DB_Part1.csv</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Reference-level approach/tracer/flow type</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Reference IDs 242; approach=E+M; tracer=; flow=S+SS</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Tatsunokuchi-yama Experimental Forest, Japan</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Official_Repository</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>FFPRI Tatsunokuchi-yama site</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>https://www2.ffpri.go.jp/labs/fwdb/sites/tatsunokuchiyamaE.htm</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Precipitation and runoff data record</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>FFPRI page lists daily precipitation and daily runoff records for Kita-dani and Minami-dani.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Tatsunokuchi-yama Experimental Forest, Japan</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Official_Repository</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>FFPRI FWDB English page</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>https://www2.ffpri.go.jp/labs/fwdb/indexE.html</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Official database access context</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>FWDB page states forest watershed observations are provided as electronic files.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Tatsunokuchi-yama Experimental Forest, Japan</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>Publication</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
         <is>
           <t>GSA Tatsunokuchi-yama abstract</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>https://gsa.confex.com/gsa/2008AM/webprogram/Paper146376.html</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Soil moisture and groundwater observation evidence</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>Abstract documents continuous soil moisture, groundwater level and streamflow response monitoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Tatsunokuchi-yama Experimental Forest, Japan</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Official_Repository</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>FFPRI Forest Experimental Watershed Database</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>https://www2.ffpri.go.jp/labs/fwdb/indexE.html</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Official/project repository public-data status and variable availability</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>FFPRI FWDB documents daily precipitation and runoff records for Japanese experimental watersheds; auxiliary soil/groundwater observations are publication-supported but not verified as public.</t>
         </is>
       </c>
     </row>
